--- a/cds_files/Baylor_CDS_2024-2025.xlsx
+++ b/cds_files/Baylor_CDS_2024-2025.xlsx
@@ -434,7 +434,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14915</v>
+        <v>14785</v>
       </c>
     </row>
     <row r="5">

--- a/cds_files/Baylor_CDS_2024-2025.xlsx
+++ b/cds_files/Baylor_CDS_2024-2025.xlsx
@@ -499,7 +499,7 @@
         <v>0.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.98</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.02</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="5">

--- a/cds_files/Baylor_CDS_2024-2025.xlsx
+++ b/cds_files/Baylor_CDS_2024-2025.xlsx
@@ -499,7 +499,7 @@
         <v>0.98</v>
       </c>
       <c r="C3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>0.02</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5">
